--- a/luban-excels/bak/xlsx/__tables__.xlsx
+++ b/luban-excels/bak/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -149,13 +149,40 @@
     <t>GameDevelopConfig@Main.xlsx</t>
   </si>
   <si>
-    <t>TbRarity</t>
-  </si>
-  <si>
-    <t>Rarity</t>
-  </si>
-  <si>
-    <t>Rarity@Main.xlsx</t>
+    <t>TbRarityUI</t>
+  </si>
+  <si>
+    <t>RarityUI</t>
+  </si>
+  <si>
+    <t>RarityUI@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbTabGroup</t>
+  </si>
+  <si>
+    <t>TabGroup</t>
+  </si>
+  <si>
+    <t>TabGroup@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbDogReaction</t>
+  </si>
+  <si>
+    <t>DogReaction</t>
+  </si>
+  <si>
+    <t>DogReaction@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbEquipmentSlotConfig</t>
+  </si>
+  <si>
+    <t>EquipmentSlotConfig</t>
+  </si>
+  <si>
+    <t>EquipmentSlotConfig@Main.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1112,12 +1139,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.1111111111111" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.6666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.6666666666667" style="2" customWidth="1"/>
     <col min="5" max="5" width="47.1111111111111" style="2" customWidth="1"/>
     <col min="6" max="6" width="114.222222222222" style="2" customWidth="1"/>
@@ -1310,6 +1337,48 @@
         <v>42</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/bak/xlsx/__tables__.xlsx
+++ b/luban-excels/bak/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -183,6 +183,15 @@
   </si>
   <si>
     <t>EquipmentSlotConfig@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbDesktopActivityState</t>
+  </si>
+  <si>
+    <t>DesktopActivityState</t>
+  </si>
+  <si>
+    <t>DesktopActivityState@Main.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1379,6 +1388,20 @@
         <v>51</v>
       </c>
     </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/bak/xlsx/__tables__.xlsx
+++ b/luban-excels/bak/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -110,7 +110,58 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t/>
+    <t>TbDogSkin</t>
+  </si>
+  <si>
+    <t>DogSkin</t>
+  </si>
+  <si>
+    <t>DogSkin@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbPayTable</t>
+  </si>
+  <si>
+    <t>PayTable</t>
+  </si>
+  <si>
+    <t>PayTable@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbGameDevelopConfig</t>
+  </si>
+  <si>
+    <t>GameDevelopConfig</t>
+  </si>
+  <si>
+    <t>GameDevelopConfig@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbRarityUI</t>
+  </si>
+  <si>
+    <t>RarityUI</t>
+  </si>
+  <si>
+    <t>RarityUI@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbDogReaction</t>
+  </si>
+  <si>
+    <t>DogReaction</t>
+  </si>
+  <si>
+    <t>DogReaction@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbDesktopActivityState</t>
+  </si>
+  <si>
+    <t>DesktopActivityState</t>
+  </si>
+  <si>
+    <t>DesktopActivityState@Main.xlsx</t>
   </si>
   <si>
     <t>TbItem</t>
@@ -119,43 +170,7 @@
     <t>Item</t>
   </si>
   <si>
-    <t>Item@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbDogSkin</t>
-  </si>
-  <si>
-    <t>DogSkin</t>
-  </si>
-  <si>
-    <t>DogSkin@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbPayTable</t>
-  </si>
-  <si>
-    <t>PayTable</t>
-  </si>
-  <si>
-    <t>PayTable@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbGameDevelopConfig</t>
-  </si>
-  <si>
-    <t>GameDevelopConfig</t>
-  </si>
-  <si>
-    <t>GameDevelopConfig@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbRarityUI</t>
-  </si>
-  <si>
-    <t>RarityUI</t>
-  </si>
-  <si>
-    <t>RarityUI@Main.xlsx</t>
+    <t>Item@Items.xlsx</t>
   </si>
   <si>
     <t>TbTabGroup</t>
@@ -164,16 +179,7 @@
     <t>TabGroup</t>
   </si>
   <si>
-    <t>TabGroup@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbDogReaction</t>
-  </si>
-  <si>
-    <t>DogReaction</t>
-  </si>
-  <si>
-    <t>DogReaction@Main.xlsx</t>
+    <t>TabGroup@Items.xlsx</t>
   </si>
   <si>
     <t>TbEquipmentSlotConfig</t>
@@ -182,16 +188,52 @@
     <t>EquipmentSlotConfig</t>
   </si>
   <si>
-    <t>EquipmentSlotConfig@Main.xlsx</t>
-  </si>
-  <si>
-    <t>TbDesktopActivityState</t>
-  </si>
-  <si>
-    <t>DesktopActivityState</t>
-  </si>
-  <si>
-    <t>DesktopActivityState@Main.xlsx</t>
+    <t>EquipmentSlotConfig@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbBlindBox</t>
+  </si>
+  <si>
+    <t>BlindBox</t>
+  </si>
+  <si>
+    <t>BlindBox@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbBlindBoxSchedule</t>
+  </si>
+  <si>
+    <t>BlindBoxSchedule</t>
+  </si>
+  <si>
+    <t>BlindBoxSchedule@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbBlindBoxRarityRate</t>
+  </si>
+  <si>
+    <t>BlindBoxRarityRate</t>
+  </si>
+  <si>
+    <t>BlindBoxRarityRate@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbBlindBoxRevealPath</t>
+  </si>
+  <si>
+    <t>BlindBoxRevealPath</t>
+  </si>
+  <si>
+    <t>BlindBoxRevealPath@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbBlindBoxVisual</t>
+  </si>
+  <si>
+    <t>BlindBoxVisual</t>
+  </si>
+  <si>
+    <t>BlindBoxVisual@Items.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1148,14 +1190,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.1111111111111" style="2" customWidth="1"/>
     <col min="3" max="3" width="26" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.6666666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="47.1111111111111" style="2" customWidth="1"/>
+    <col min="5" max="5" width="50.5555555555556" style="2" customWidth="1"/>
     <col min="6" max="6" width="114.222222222222" style="2" customWidth="1"/>
     <col min="7" max="7" width="40.4444444444444" style="2" customWidth="1"/>
     <col min="8" max="8" width="70" style="2" customWidth="1"/>
@@ -1256,150 +1298,204 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="B9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D9" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>48</v>
+      <c r="A10" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="2" t="s">
         <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/__tables__.xlsx
+++ b/luban-excels/bak/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -162,6 +162,15 @@
   </si>
   <si>
     <t>DesktopActivityState@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbBGMList</t>
+  </si>
+  <si>
+    <t>BGMList</t>
+  </si>
+  <si>
+    <t>BGMList@Main.xlsx</t>
   </si>
   <si>
     <t>TbItem</t>
@@ -1190,7 +1199,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1382,22 +1391,22 @@
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1496,6 +1505,20 @@
       </c>
       <c r="E18" s="2" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/__tables__.xlsx
+++ b/luban-excels/bak/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -171,6 +171,24 @@
   </si>
   <si>
     <t>BGMList@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbAchievement</t>
+  </si>
+  <si>
+    <t>Achievement</t>
+  </si>
+  <si>
+    <t>Achievement@Main.xlsx</t>
+  </si>
+  <si>
+    <t>TbPlayerStatistic</t>
+  </si>
+  <si>
+    <t>PlayerStatistic</t>
+  </si>
+  <si>
+    <t>PlayerStatistic@Main.xlsx</t>
   </si>
   <si>
     <t>TbItem</t>
@@ -1199,7 +1217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1405,36 +1423,36 @@
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
+      <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="B13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>53</v>
+      <c r="A13" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1519,6 +1537,34 @@
       </c>
       <c r="E19" s="2" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/__tables__.xlsx
+++ b/luban-excels/bak/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
@@ -261,6 +261,15 @@
   </si>
   <si>
     <t>BlindBoxVisual@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbLinkTree</t>
+  </si>
+  <si>
+    <t>LinkTree</t>
+  </si>
+  <si>
+    <t>LinkTree@Items.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1226,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1567,6 +1576,20 @@
         <v>77</v>
       </c>
     </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/bak/xlsx/__tables__.xlsx
+++ b/luban-excels/bak/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
   <si>
     <t>##var</t>
   </si>
@@ -270,6 +270,15 @@
   </si>
   <si>
     <t>LinkTree@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbSteamItemDef</t>
+  </si>
+  <si>
+    <t>SteamItemDef</t>
+  </si>
+  <si>
+    <t>SteamItemDef@Items.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1235,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1590,6 +1599,20 @@
         <v>80</v>
       </c>
     </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/bak/xlsx/__tables__.xlsx
+++ b/luban-excels/bak/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -279,6 +279,15 @@
   </si>
   <si>
     <t>SteamItemDef@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbSteamItemDefIdRange</t>
+  </si>
+  <si>
+    <t>SteamItemDefIdRange</t>
+  </si>
+  <si>
+    <t>SteamItemDefIdRange@Items.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1613,6 +1622,20 @@
         <v>83</v>
       </c>
     </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/luban-excels/bak/xlsx/__tables__.xlsx
+++ b/luban-excels/bak/xlsx/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
   <si>
     <t>##var</t>
   </si>
@@ -191,6 +191,15 @@
     <t>PlayerStatistic@Main.xlsx</t>
   </si>
   <si>
+    <t>TbInteractionHintConfig</t>
+  </si>
+  <si>
+    <t>InteractionHintConfig</t>
+  </si>
+  <si>
+    <t>InteractionHintConfig@Main.xlsx</t>
+  </si>
+  <si>
     <t>TbItem</t>
   </si>
   <si>
@@ -288,6 +297,15 @@
   </si>
   <si>
     <t>SteamItemDefIdRange@Items.xlsx</t>
+  </si>
+  <si>
+    <t>TbRefreshmentConfig</t>
+  </si>
+  <si>
+    <t>RefreshmentConfig</t>
+  </si>
+  <si>
+    <t>RefreshmentConfig@Items.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1262,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
@@ -1478,22 +1496,22 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="B14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1634,6 +1652,34 @@
       </c>
       <c r="E24" s="2" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
